--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.21955349136559</v>
+        <v>1.985677442346908</v>
       </c>
       <c r="D2" t="n">
-        <v>11.50802547094144</v>
+        <v>1.870054139027983</v>
       </c>
       <c r="E2" t="n">
-        <v>9.968595296512744</v>
+        <v>1.619896735683321</v>
       </c>
       <c r="F2" t="n">
-        <v>10.15981469769283</v>
+        <v>1.650969888375085</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.76406446625612</v>
+        <v>4.024160475766619</v>
       </c>
       <c r="D3" t="n">
-        <v>28.14446857041558</v>
+        <v>4.573476142692533</v>
       </c>
       <c r="E3" t="n">
-        <v>9.968595296512744</v>
+        <v>1.619896735683321</v>
       </c>
       <c r="F3" t="n">
-        <v>10.15981469769283</v>
+        <v>1.650969888375085</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.1110596046374</v>
+        <v>5.543047185753577</v>
       </c>
       <c r="D4" t="n">
-        <v>34.39292529162553</v>
+        <v>5.588850359889149</v>
       </c>
       <c r="E4" t="n">
-        <v>9.968595296512744</v>
+        <v>1.619896735683321</v>
       </c>
       <c r="F4" t="n">
-        <v>10.15981469769283</v>
+        <v>1.650969888375085</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.12821919518567</v>
+        <v>6.195835619217672</v>
       </c>
       <c r="D5" t="n">
-        <v>38.0006139667889</v>
+        <v>6.175099769603198</v>
       </c>
       <c r="E5" t="n">
-        <v>9.968595296512744</v>
+        <v>1.619896735683321</v>
       </c>
       <c r="F5" t="n">
-        <v>10.15981469769283</v>
+        <v>1.650969888375085</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
